--- a/data/trans_dic/P17G_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,14</t>
+          <t>0,46; 3,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,28</t>
+          <t>0,25; 2,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,14</t>
+          <t>0,24; 2,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,34</t>
+          <t>0,23; 2,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,23</t>
+          <t>0,23; 2,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,9</t>
+          <t>0,37; 3,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,54</t>
+          <t>0,3; 1,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,24</t>
+          <t>0,56; 2,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,75</t>
+          <t>0,37; 1,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,29</t>
+          <t>0,47; 3,15</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,15</t>
+          <t>0,45; 2,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,73</t>
+          <t>0,27; 1,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,73</t>
+          <t>1,17; 3,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,76</t>
+          <t>0,72; 4,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,17</t>
+          <t>0,88; 3,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,69</t>
+          <t>0,48; 2,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,06</t>
+          <t>1,33; 3,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,85</t>
+          <t>1,23; 4,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,26</t>
+          <t>0,82; 2,2</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,76</t>
+          <t>0,58; 1,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,42</t>
+          <t>1,51; 3,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,06</t>
+          <t>1,38; 3,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,65</t>
+          <t>0,58; 2,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,95</t>
+          <t>0,42; 1,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,63</t>
+          <t>0,65; 2,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,4</t>
+          <t>0,87; 3,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,9</t>
+          <t>0,71; 2,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,02</t>
+          <t>0,69; 2,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,01</t>
+          <t>0,93; 3,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,92</t>
+          <t>1,63; 3,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,25</t>
+          <t>0,92; 2,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,13</t>
+          <t>0,75; 2,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,39</t>
+          <t>1,0; 2,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,2</t>
+          <t>1,48; 3,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,71</t>
+          <t>0,57; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,78</t>
+          <t>0,54; 2,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,4</t>
+          <t>1,42; 4,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,86</t>
+          <t>0,54; 2,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,56</t>
+          <t>1,08; 3,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,38</t>
+          <t>0,16; 1,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,05</t>
+          <t>0,96; 3,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,75</t>
+          <t>1,83; 3,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,67</t>
+          <t>1,12; 2,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,72</t>
+          <t>0,5; 1,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,15</t>
+          <t>1,42; 3,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,87</t>
+          <t>1,21; 2,92</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,71</t>
+          <t>1,28; 4,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,42</t>
+          <t>0,99; 4,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,03</t>
+          <t>1,07; 3,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,74</t>
+          <t>0,68; 2,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,51</t>
+          <t>1,18; 4,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,22</t>
+          <t>0,25; 2,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,45</t>
+          <t>1,2; 4,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,37</t>
+          <t>1,4; 3,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,81</t>
+          <t>1,63; 3,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,95</t>
+          <t>0,81; 2,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,6</t>
+          <t>1,4; 3,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,67</t>
+          <t>1,26; 2,63</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,34</t>
+          <t>0,95; 4,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,94</t>
+          <t>0,66; 4,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,83</t>
+          <t>0,31; 2,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,54</t>
+          <t>1,47; 4,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,22</t>
+          <t>0,55; 3,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,98</t>
+          <t>0,82; 3,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,87</t>
+          <t>1,11; 5,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,06</t>
+          <t>0,28; 2,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,98</t>
+          <t>1,01; 3,11</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,45</t>
+          <t>1,07; 3,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,34</t>
+          <t>0,97; 3,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,59</t>
+          <t>0,79; 2,5</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,53</t>
+          <t>0,43; 4,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,86</t>
+          <t>0,65; 5,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,6</t>
+          <t>0,42; 2,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,72</t>
+          <t>0,32; 2,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,75</t>
+          <t>0,6; 3,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,6</t>
+          <t>0,32; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,39</t>
+          <t>1,29; 3,48</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,89</t>
+          <t>0,52; 2,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,36</t>
+          <t>0,52; 2,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,81</t>
+          <t>0,66; 2,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,54</t>
+          <t>1,11; 2,62</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,88</t>
+          <t>1,03; 1,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1707,52 +1707,52 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,36</t>
+          <t>1,37; 2,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,33</t>
+          <t>1,26; 2,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,12</t>
+          <t>1,27; 2,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,66</t>
+          <t>0,9; 1,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,47</t>
+          <t>1,4; 2,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,84</t>
+          <t>1,23; 1,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,61</t>
+          <t>1,02; 1,6</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,23</t>
+          <t>1,52; 2,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,31</t>
+          <t>1,62; 2,35</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha acudido a un médico privado en su última visita</t>
+          <t>Población que consultó en las últimas 2 semanas a un/a médico/a privado/a (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 12039</t>
+          <t>0; 10733</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2048; 14173</t>
+          <t>2054; 14751</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1048; 9553</t>
+          <t>1056; 11016</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 18605</t>
+          <t>0; 19804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1109; 9999</t>
+          <t>1118; 9416</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>989; 9958</t>
+          <t>996; 10468</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>924; 8844</t>
+          <t>925; 7969</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1171; 12212</t>
+          <t>1155; 12134</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2117; 14820</t>
+          <t>2886; 15007</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5088; 19670</t>
+          <t>4955; 19141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3062; 14231</t>
+          <t>2977; 13380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3415; 23479</t>
+          <t>3363; 22497</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3356; 15803</t>
+          <t>3318; 15908</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1837; 11837</t>
+          <t>1859; 10942</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6237; 21970</t>
+          <t>6889; 23493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3368; 20164</t>
+          <t>3068; 20977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5168; 19808</t>
+          <t>5530; 19669</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3101; 16191</t>
+          <t>2922; 15708</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7411; 22757</t>
+          <t>7475; 22373</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7018; 24751</t>
+          <t>6264; 24901</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11376; 30801</t>
+          <t>11130; 29972</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6785; 22644</t>
+          <t>7450; 21617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16890; 39345</t>
+          <t>17339; 38436</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12605; 37885</t>
+          <t>12897; 36778</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3647; 16877</t>
+          <t>3729; 18316</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2853; 13181</t>
+          <t>2824; 12414</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3984; 17595</t>
+          <t>4330; 17820</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4456; 18226</t>
+          <t>4651; 18803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5775; 19944</t>
+          <t>4909; 20059</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5620; 21335</t>
+          <t>4887; 20586</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6272; 19763</t>
+          <t>6137; 19889</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8632; 21260</t>
+          <t>8826; 21257</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11231; 29760</t>
+          <t>12241; 31541</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10419; 29442</t>
+          <t>10424; 29663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13029; 31651</t>
+          <t>13233; 32040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16561; 34555</t>
+          <t>15980; 34267</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3344; 14038</t>
+          <t>2930; 13878</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3962; 17054</t>
+          <t>3309; 18039</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9253; 28242</t>
+          <t>9088; 27734</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5248; 25357</t>
+          <t>4805; 25439</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5319; 18364</t>
+          <t>5570; 19217</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>963; 8442</t>
+          <t>965; 9468</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5395; 19679</t>
+          <t>6203; 21232</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12808; 26746</t>
+          <t>13052; 26941</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10900; 27587</t>
+          <t>11578; 28279</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5323; 21066</t>
+          <t>6138; 20643</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18228; 40499</t>
+          <t>18248; 41432</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19101; 45938</t>
+          <t>19322; 46727</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5313; 18205</t>
+          <t>4961; 18566</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4491; 18806</t>
+          <t>4198; 20230</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5391; 19237</t>
+          <t>5106; 17556</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3989; 15405</t>
+          <t>3825; 15267</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5008; 18225</t>
+          <t>4769; 18102</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1044; 9888</t>
+          <t>1109; 10328</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6163; 21771</t>
+          <t>5854; 22107</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8165; 18431</t>
+          <t>7689; 18554</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12220; 30141</t>
+          <t>12888; 31144</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7205; 25660</t>
+          <t>7094; 24953</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13923; 34805</t>
+          <t>13568; 34784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14712; 29572</t>
+          <t>13975; 29143</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2675; 12630</t>
+          <t>2751; 12622</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2077; 15193</t>
+          <t>2027; 15041</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>920; 9385</t>
+          <t>1027; 9533</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5707; 16691</t>
+          <t>5388; 16011</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1825; 11040</t>
+          <t>1874; 10965</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2992; 13928</t>
+          <t>2880; 13701</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4743; 18366</t>
+          <t>4180; 19108</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2184; 12535</t>
+          <t>1682; 12642</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5651; 18897</t>
+          <t>6382; 19729</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7011; 22699</t>
+          <t>7029; 22479</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7434; 23630</t>
+          <t>6885; 22076</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8167; 25282</t>
+          <t>7741; 24417</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>890; 9507</t>
+          <t>905; 9090</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4863</t>
+          <t>0; 4488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1789; 12403</t>
+          <t>1649; 12879</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1217; 7328</t>
+          <t>1194; 7901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1075; 9083</t>
+          <t>1063; 9654</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3156; 14413</t>
+          <t>2314; 13659</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1264; 10302</t>
+          <t>1262; 10481</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5350; 14410</t>
+          <t>5471; 14808</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2985; 15714</t>
+          <t>2815; 15254</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3160; 14910</t>
+          <t>3282; 14913</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3964; 18309</t>
+          <t>4328; 18720</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7913; 17986</t>
+          <t>7848; 18512</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33859; 61432</t>
+          <t>33614; 62190</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31342; 60654</t>
+          <t>31422; 60509</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45609; 79830</t>
+          <t>46226; 76927</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42980; 80472</t>
+          <t>43574; 80559</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>41338; 71712</t>
+          <t>42750; 74119</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32042; 58504</t>
+          <t>31770; 61314</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51758; 86960</t>
+          <t>49277; 84521</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>61378; 95841</t>
+          <t>61488; 97143</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>83093; 122514</t>
+          <t>81811; 123182</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70533; 111291</t>
+          <t>70865; 110733</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>104946; 153876</t>
+          <t>105130; 150567</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>112788; 164489</t>
+          <t>115007; 167168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P17G_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P17G_R2-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,27</t>
+          <t>0,46; 3,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,63</t>
+          <t>0,25; 2,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,01</t>
+          <t>0,24; 2,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,46</t>
+          <t>0,23; 2,35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,01</t>
+          <t>0,23; 2,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,87</t>
+          <t>0,37; 3,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,56</t>
+          <t>0,3; 1,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,18</t>
+          <t>0,56; 2,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,64</t>
+          <t>0,36; 1,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,15</t>
+          <t>0,4; 2,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,17</t>
+          <t>0,47; 2,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,6</t>
+          <t>0,27; 1,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,99</t>
+          <t>0,98; 3,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,95</t>
+          <t>0,66; 4,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,14</t>
+          <t>0,83; 3,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,61</t>
+          <t>0,51; 2,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,99</t>
+          <t>1,48; 4,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,88</t>
+          <t>1,48; 4,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,2</t>
+          <t>0,82; 2,23</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,68</t>
+          <t>0,52; 1,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,34</t>
+          <t>1,51; 3,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 3,94</t>
+          <t>1,37; 3,73</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,87</t>
+          <t>0,58; 2,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,84</t>
+          <t>0,42; 1,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,66</t>
+          <t>0,57; 2,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,51</t>
+          <t>1,23; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,92</t>
+          <t>0,86; 3,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,92</t>
+          <t>0,76; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,02</t>
+          <t>0,96; 3,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,92</t>
+          <t>1,55; 3,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,38</t>
+          <t>0,92; 2,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,15</t>
+          <t>0,75; 2,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,42</t>
+          <t>1,0; 2,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,18</t>
+          <t>1,59; 3,31</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,68</t>
+          <t>0,71; 2,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,95</t>
+          <t>0,54; 2,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,32</t>
+          <t>1,44; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,87</t>
+          <t>1,21; 3,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,73</t>
+          <t>0,99; 3,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,54</t>
+          <t>0,16; 1,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,29</t>
+          <t>0,97; 3,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,78</t>
+          <t>1,99; 4,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,74</t>
+          <t>1,09; 2,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,68</t>
+          <t>0,51; 1,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,22</t>
+          <t>1,38; 3,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,92</t>
+          <t>1,8; 3,38</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,8</t>
+          <t>1,39; 4,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,76</t>
+          <t>1,02; 4,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,68</t>
+          <t>1,11; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,72</t>
+          <t>0,63; 2,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,48</t>
+          <t>1,08; 4,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,32</t>
+          <t>0,23; 2,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,52</t>
+          <t>1,17; 4,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,39</t>
+          <t>1,51; 3,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,94</t>
+          <t>1,57; 3,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,87</t>
+          <t>0,83; 2,82</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,6</t>
+          <t>1,41; 3,69</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,63</t>
+          <t>1,27; 2,58</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,34</t>
+          <t>0,94; 4,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,89</t>
+          <t>0,67; 5,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,88</t>
+          <t>0,28; 2,92</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,36</t>
+          <t>1,39; 4,31</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,2</t>
+          <t>0,56; 3,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,91</t>
+          <t>0,84; 3,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,07</t>
+          <t>1,08; 4,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,08</t>
+          <t>0,88; 2,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,11</t>
+          <t>1,02; 3,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,42</t>
+          <t>1,08; 3,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,12</t>
+          <t>0,97; 3,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,5</t>
+          <t>1,35; 2,97</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,33</t>
+          <t>0,43; 4,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,04</t>
+          <t>0,65; 4,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,8</t>
+          <t>0,33; 2,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,55</t>
+          <t>0,59; 3,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,64</t>
+          <t>0,32; 3,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,48</t>
+          <t>1,24; 3,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,81</t>
+          <t>0,44; 2,54</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,36</t>
+          <t>0,51; 2,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,87</t>
+          <t>0,65; 2,76</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,62</t>
+          <t>1,09; 2,67</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,9</t>
+          <t>1,05; 1,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,78</t>
+          <t>0,92; 1,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,27</t>
+          <t>1,39; 2,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,33</t>
+          <t>1,36; 2,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,19</t>
+          <t>1,22; 2,1</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,74</t>
+          <t>0,86; 1,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,4</t>
+          <t>1,43; 2,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,66</t>
+          <t>1,88; 2,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 1,85</t>
+          <t>1,26; 1,87</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,6</t>
+          <t>0,99; 1,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,18</t>
+          <t>1,54; 2,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,35</t>
+          <t>1,75; 2,41</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9642</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 10733</t>
+          <t>0; 11178</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2054; 14751</t>
+          <t>2057; 15035</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1056; 11016</t>
+          <t>1053; 9435</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 19804</t>
+          <t>0; 18257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1118; 9416</t>
+          <t>1108; 10047</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>996; 10468</t>
+          <t>972; 10030</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>925; 7969</t>
+          <t>925; 8134</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1155; 12134</t>
+          <t>1330; 12970</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2886; 15007</t>
+          <t>2929; 16506</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4955; 19141</t>
+          <t>4928; 19008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2977; 13380</t>
+          <t>2942; 13325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3363; 22497</t>
+          <t>3096; 20927</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13943</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>22483</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3318; 15908</t>
+          <t>3448; 17076</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1859; 10942</t>
+          <t>1850; 11279</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6889; 23493</t>
+          <t>5770; 21537</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3068; 20977</t>
+          <t>3169; 21153</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5530; 19669</t>
+          <t>5164; 19890</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2922; 15708</t>
+          <t>3045; 16436</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7475; 22373</t>
+          <t>8279; 23470</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6264; 24901</t>
+          <t>7364; 23995</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11130; 29972</t>
+          <t>11151; 30294</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7450; 21617</t>
+          <t>6713; 22326</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17339; 38436</t>
+          <t>17328; 39545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12897; 36778</t>
+          <t>13375; 36360</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23774</t>
+          <t>28402</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3729; 18316</t>
+          <t>3691; 16814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2824; 12414</t>
+          <t>2809; 13446</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4330; 17820</t>
+          <t>3805; 17188</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4651; 18803</t>
+          <t>7660; 25853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4909; 20059</t>
+          <t>5916; 23230</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4887; 20586</t>
+          <t>5399; 20333</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6137; 19889</t>
+          <t>6301; 19697</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8826; 21257</t>
+          <t>9634; 22872</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12241; 31541</t>
+          <t>12191; 29821</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10424; 29663</t>
+          <t>10361; 28633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13233; 32040</t>
+          <t>13296; 31556</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15980; 34267</t>
+          <t>19775; 41137</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33484</t>
+          <t>35862</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2930; 13878</t>
+          <t>3655; 14380</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3309; 18039</t>
+          <t>3301; 16688</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9088; 27734</t>
+          <t>9256; 26900</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4805; 25439</t>
+          <t>8473; 24818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5570; 19217</t>
+          <t>5123; 19061</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>965; 9468</t>
+          <t>961; 8733</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6203; 21232</t>
+          <t>6237; 20287</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13052; 26941</t>
+          <t>14619; 30291</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11578; 28279</t>
+          <t>11220; 27177</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6138; 20643</t>
+          <t>6195; 21246</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18248; 41432</t>
+          <t>17760; 41820</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19322; 46727</t>
+          <t>25918; 48603</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20703</t>
+          <t>21992</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4961; 18566</t>
+          <t>5382; 18466</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4198; 20230</t>
+          <t>4318; 19420</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5106; 17556</t>
+          <t>5299; 19589</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3825; 15267</t>
+          <t>3845; 15786</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4769; 18102</t>
+          <t>4343; 18027</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1109; 10328</t>
+          <t>1042; 10133</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5854; 22107</t>
+          <t>5734; 22736</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7689; 18554</t>
+          <t>9208; 20748</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12888; 31144</t>
+          <t>12379; 31129</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7094; 24953</t>
+          <t>7203; 24532</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13568; 34784</t>
+          <t>13622; 35683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>13975; 29143</t>
+          <t>15515; 31460</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7116</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16428</t>
+          <t>17560</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2751; 12622</t>
+          <t>2732; 12406</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2027; 15041</t>
+          <t>2074; 15428</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1027; 9533</t>
+          <t>922; 9666</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5388; 16011</t>
+          <t>5658; 17504</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1874; 10965</t>
+          <t>1907; 11634</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2880; 13701</t>
+          <t>2934; 13491</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4180; 19108</t>
+          <t>4069; 18327</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1682; 12642</t>
+          <t>3852; 11612</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6382; 19729</t>
+          <t>6446; 19909</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7029; 22479</t>
+          <t>7079; 22150</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6885; 22076</t>
+          <t>6844; 22636</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7741; 24417</t>
+          <t>11368; 25120</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>9777</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>13427</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>905; 9090</t>
+          <t>897; 9501</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4488</t>
+          <t>0; 4350</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1649; 12879</t>
+          <t>1656; 11159</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1194; 7901</t>
+          <t>1020; 8588</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1063; 9654</t>
+          <t>1068; 9657</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2314; 13659</t>
+          <t>2273; 14165</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1262; 10481</t>
+          <t>1274; 12075</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5471; 14808</t>
+          <t>5765; 15725</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2815; 15254</t>
+          <t>2397; 13814</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3282; 14913</t>
+          <t>3224; 15332</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4328; 18720</t>
+          <t>4267; 17959</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7848; 18512</t>
+          <t>8392; 20623</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>79255</t>
+          <t>85324</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>138661</t>
+          <t>149368</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>33614; 62190</t>
+          <t>34362; 63320</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>31422; 60509</t>
+          <t>31284; 61554</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46226; 76927</t>
+          <t>46905; 80693</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43574; 80559</t>
+          <t>47851; 85395</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42750; 74119</t>
+          <t>41285; 70942</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31770; 61314</t>
+          <t>30292; 57277</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49277; 84521</t>
+          <t>50316; 83512</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>61488; 97143</t>
+          <t>69989; 104437</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81811; 123182</t>
+          <t>83428; 124147</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70865; 110733</t>
+          <t>68540; 107747</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105130; 150567</t>
+          <t>106017; 150857</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>115007; 167168</t>
+          <t>127400; 174814</t>
         </is>
       </c>
     </row>
